--- a/docs/d/222/inyear.xlsx
+++ b/docs/d/222/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 61 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 57 clubs short</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" s="6" t="n">
         <v>10</v>
@@ -1197,8 +1197,8 @@
       <c r="Y5" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z5" s="9" t="n">
-        <v>0</v>
+      <c r="Z5" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA5" s="10" t="n">
         <v>1</v>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>10</v>
@@ -2361,8 +2361,8 @@
       <c r="Y17" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z17" s="9" t="n">
-        <v>0</v>
+      <c r="Z17" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA17" s="10" t="n">
         <v>1</v>
@@ -6891,7 +6891,7 @@
         </is>
       </c>
       <c r="P64" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q64" s="9" t="n">
         <v>1</v>
@@ -9122,7 +9122,7 @@
         </is>
       </c>
       <c r="P87" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q87" s="9" t="n">
         <v>0</v>
@@ -9566,7 +9566,7 @@
         </is>
       </c>
       <c r="E92" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F92" s="6" t="n">
         <v>10</v>
@@ -9636,8 +9636,8 @@
       <c r="Y92" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z92" s="9" t="n">
-        <v>0</v>
+      <c r="Z92" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA92" s="10" t="n">
         <v>1</v>
@@ -9857,7 +9857,7 @@
         </is>
       </c>
       <c r="E95" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F95" s="6" t="n">
         <v>10</v>
@@ -9927,8 +9927,8 @@
       <c r="Y95" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z95" s="9" t="n">
-        <v>0</v>
+      <c r="Z95" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA95" s="10" t="n">
         <v>1</v>
@@ -12350,7 +12350,7 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -12449,7 +12449,7 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -12977,7 +12977,7 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="E21" t="n">
         <v>1</v>
@@ -13010,7 +13010,7 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>

--- a/docs/d/222/inyear.xlsx
+++ b/docs/d/222/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/222/inyear.xlsx
+++ b/docs/d/222/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (99 days) - 13 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 13 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 57 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 55 clubs short</t>
         </is>
       </c>
     </row>
@@ -1030,7 +1030,7 @@
         </is>
       </c>
       <c r="E4" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F4" s="6" t="n">
         <v>10</v>
@@ -1073,8 +1073,8 @@
       <c r="P4" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="Q4" s="9" t="n">
-        <v>1</v>
+      <c r="Q4" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R4" s="9" t="n">
         <v>0</v>
@@ -1806,7 +1806,7 @@
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" s="6" t="n">
         <v>10</v>
@@ -1858,8 +1858,8 @@
       <c r="S12" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T12" s="9" t="n">
-        <v>0</v>
+      <c r="T12" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U12" s="9" t="n">
         <v>0</v>
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F13" s="6" t="n">
         <v>10</v>
@@ -1944,16 +1944,16 @@
         </is>
       </c>
       <c r="P13" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q13" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" s="10" t="n">
         <v>2</v>
-      </c>
-      <c r="Q13" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" s="9" t="n">
-        <v>1</v>
       </c>
       <c r="T13" s="10" t="n">
         <v>1</v>
@@ -3261,7 +3261,7 @@
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F27" s="6" t="n">
         <v>10</v>
@@ -3313,8 +3313,8 @@
       <c r="S27" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T27" s="9" t="n">
-        <v>0</v>
+      <c r="T27" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U27" s="9" t="n">
         <v>0</v>
@@ -4281,7 +4281,7 @@
         <v>0</v>
       </c>
       <c r="S37" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T37" s="9" t="n">
         <v>0</v>
@@ -4951,7 +4951,7 @@
         </is>
       </c>
       <c r="P44" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q44" s="9" t="n">
         <v>0</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="E67" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F67" s="6" t="n">
         <v>10</v>
@@ -7193,8 +7193,8 @@
       <c r="S67" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T67" s="9" t="n">
-        <v>0</v>
+      <c r="T67" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U67" s="9" t="n">
         <v>0</v>
@@ -9178,7 +9178,7 @@
         </is>
       </c>
       <c r="E88" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F88" s="6" t="n">
         <v>10</v>
@@ -9248,8 +9248,8 @@
       <c r="Y88" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z88" s="9" t="n">
-        <v>0</v>
+      <c r="Z88" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA88" s="10" t="n">
         <v>1</v>
@@ -9275,7 +9275,7 @@
         </is>
       </c>
       <c r="E89" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F89" s="6" t="n">
         <v>10</v>
@@ -9289,13 +9289,13 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L89" s="7" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         <v>0</v>
       </c>
       <c r="V89" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W89" s="9" t="n">
         <v>0</v>
@@ -9345,8 +9345,8 @@
       <c r="Y89" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z89" s="9" t="n">
-        <v>0</v>
+      <c r="Z89" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA89" s="10" t="n">
         <v>1</v>
@@ -10550,13 +10550,13 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L102" s="4" t="inlineStr">
         <is>
@@ -10598,7 +10598,7 @@
         <v>4</v>
       </c>
       <c r="W102" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X102" s="10" t="n">
         <v>4</v>
@@ -11409,7 +11409,7 @@
         </is>
       </c>
       <c r="E111" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F111" s="6" t="n">
         <v>10</v>
@@ -11449,11 +11449,11 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P111" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q111" s="9" t="n">
-        <v>1</v>
+      <c r="P111" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q111" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R111" s="9" t="n">
         <v>0</v>
@@ -12129,7 +12129,7 @@
         </is>
       </c>
       <c r="P118" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q118" s="9" t="n">
         <v>1</v>
@@ -12350,13 +12350,13 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -12416,7 +12416,7 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -12515,7 +12515,7 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -12812,7 +12812,7 @@
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -12944,7 +12944,7 @@
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="E20" t="n">
         <v>1</v>
@@ -13109,7 +13109,7 @@
         <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>

--- a/docs/d/222/inyear.xlsx
+++ b/docs/d/222/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:22 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>276 days remain until 30 June 2027, when these scores become final.</t>
+          <t>269 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 13 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 13 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 55 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 23 clubs short</t>
         </is>
       </c>
     </row>
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="P3" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" s="9" t="n">
         <v>1</v>
@@ -983,7 +983,7 @@
         <v>0</v>
       </c>
       <c r="S3" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T3" s="10" t="n">
         <v>1</v>
@@ -1806,7 +1806,7 @@
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F12" s="6" t="n">
         <v>10</v>
@@ -1876,8 +1876,8 @@
       <c r="Y12" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z12" s="9" t="n">
-        <v>0</v>
+      <c r="Z12" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA12" s="10" t="n">
         <v>1</v>
@@ -2138,7 +2138,7 @@
         </is>
       </c>
       <c r="P15" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q15" s="9" t="n">
         <v>1</v>
@@ -2194,7 +2194,7 @@
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" s="6" t="n">
         <v>10</v>
@@ -2264,8 +2264,8 @@
       <c r="Y16" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z16" s="9" t="n">
-        <v>0</v>
+      <c r="Z16" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA16" s="10" t="n">
         <v>1</v>
@@ -2652,8 +2652,8 @@
       <c r="Y20" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z20" s="9" t="n">
-        <v>0</v>
+      <c r="Z20" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA20" s="9" t="n">
         <v>0</v>
@@ -2679,7 +2679,7 @@
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F21" s="6" t="n">
         <v>10</v>
@@ -2749,8 +2749,8 @@
       <c r="Y21" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z21" s="9" t="n">
-        <v>0</v>
+      <c r="Z21" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA21" s="10" t="n">
         <v>1</v>
@@ -2970,7 +2970,7 @@
         </is>
       </c>
       <c r="E24" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24" s="6" t="n">
         <v>10</v>
@@ -3011,7 +3011,7 @@
         </is>
       </c>
       <c r="P24" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q24" s="9" t="n">
         <v>1</v>
@@ -3022,8 +3022,8 @@
       <c r="S24" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T24" s="9" t="n">
-        <v>0</v>
+      <c r="T24" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U24" s="9" t="n">
         <v>0</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="P26" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q26" s="9" t="n">
         <v>1</v>
@@ -3455,7 +3455,7 @@
         </is>
       </c>
       <c r="E29" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F29" s="6" t="n">
         <v>10</v>
@@ -3469,17 +3469,17 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L29" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>6</v>
+      </c>
+      <c r="L29" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M29" s="8" t="n">
@@ -3513,11 +3513,11 @@
       <c r="U29" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V29" s="9" t="n">
-        <v>1</v>
+      <c r="V29" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W29" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X29" s="10" t="n">
         <v>6</v>
@@ -3525,8 +3525,8 @@
       <c r="Y29" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z29" s="9" t="n">
-        <v>0</v>
+      <c r="Z29" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA29" s="10" t="n">
         <v>1</v>
@@ -3552,7 +3552,7 @@
         </is>
       </c>
       <c r="E30" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F30" s="6" t="n">
         <v>10</v>
@@ -3622,8 +3622,8 @@
       <c r="Y30" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z30" s="9" t="n">
-        <v>0</v>
+      <c r="Z30" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA30" s="10" t="n">
         <v>1</v>
@@ -3843,7 +3843,7 @@
         </is>
       </c>
       <c r="E33" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F33" s="6" t="n">
         <v>10</v>
@@ -3913,8 +3913,8 @@
       <c r="Y33" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z33" s="9" t="n">
-        <v>0</v>
+      <c r="Z33" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA33" s="10" t="n">
         <v>1</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="E35" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F35" s="6" t="n">
         <v>10</v>
@@ -4107,8 +4107,8 @@
       <c r="Y35" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z35" s="9" t="n">
-        <v>0</v>
+      <c r="Z35" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA35" s="10" t="n">
         <v>1</v>
@@ -4328,7 +4328,7 @@
         </is>
       </c>
       <c r="E38" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F38" s="6" t="n">
         <v>10</v>
@@ -4342,13 +4342,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
@@ -4386,11 +4386,11 @@
       <c r="U38" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V38" s="9" t="n">
-        <v>0</v>
+      <c r="V38" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W38" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X38" s="10" t="n">
         <v>7</v>
@@ -5783,7 +5783,7 @@
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F53" s="6" t="n">
         <v>10</v>
@@ -5853,8 +5853,8 @@
       <c r="Y53" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z53" s="9" t="n">
-        <v>0</v>
+      <c r="Z53" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA53" s="10" t="n">
         <v>1</v>
@@ -5880,7 +5880,7 @@
         </is>
       </c>
       <c r="E54" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F54" s="6" t="n">
         <v>10</v>
@@ -5950,8 +5950,8 @@
       <c r="Y54" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z54" s="9" t="n">
-        <v>0</v>
+      <c r="Z54" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA54" s="10" t="n">
         <v>1</v>
@@ -6144,8 +6144,8 @@
       <c r="Y56" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z56" s="9" t="n">
-        <v>0</v>
+      <c r="Z56" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA56" s="9" t="n">
         <v>0</v>
@@ -6171,7 +6171,7 @@
         </is>
       </c>
       <c r="E57" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F57" s="6" t="n">
         <v>10</v>
@@ -6241,8 +6241,8 @@
       <c r="Y57" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z57" s="9" t="n">
-        <v>0</v>
+      <c r="Z57" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA57" s="10" t="n">
         <v>1</v>
@@ -6268,7 +6268,7 @@
         </is>
       </c>
       <c r="E58" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F58" s="6" t="n">
         <v>10</v>
@@ -6338,8 +6338,8 @@
       <c r="Y58" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z58" s="9" t="n">
-        <v>0</v>
+      <c r="Z58" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA58" s="10" t="n">
         <v>1</v>
@@ -6365,7 +6365,7 @@
         </is>
       </c>
       <c r="E59" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F59" s="6" t="n">
         <v>10</v>
@@ -6435,8 +6435,8 @@
       <c r="Y59" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z59" s="9" t="n">
-        <v>0</v>
+      <c r="Z59" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA59" s="10" t="n">
         <v>1</v>
@@ -6559,7 +6559,7 @@
         </is>
       </c>
       <c r="E61" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F61" s="6" t="n">
         <v>10</v>
@@ -6629,8 +6629,8 @@
       <c r="Y61" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z61" s="9" t="n">
-        <v>0</v>
+      <c r="Z61" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA61" s="10" t="n">
         <v>1</v>
@@ -7238,7 +7238,7 @@
         </is>
       </c>
       <c r="E68" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F68" s="6" t="n">
         <v>10</v>
@@ -7308,8 +7308,8 @@
       <c r="Y68" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z68" s="9" t="n">
-        <v>0</v>
+      <c r="Z68" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA68" s="10" t="n">
         <v>1</v>
@@ -7335,7 +7335,7 @@
         </is>
       </c>
       <c r="E69" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F69" s="6" t="n">
         <v>10</v>
@@ -7405,8 +7405,8 @@
       <c r="Y69" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z69" s="9" t="n">
-        <v>0</v>
+      <c r="Z69" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA69" s="10" t="n">
         <v>1</v>
@@ -7432,7 +7432,7 @@
         </is>
       </c>
       <c r="E70" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F70" s="6" t="n">
         <v>10</v>
@@ -7502,8 +7502,8 @@
       <c r="Y70" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z70" s="9" t="n">
-        <v>0</v>
+      <c r="Z70" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA70" s="10" t="n">
         <v>1</v>
@@ -7626,7 +7626,7 @@
         </is>
       </c>
       <c r="E72" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F72" s="6" t="n">
         <v>10</v>
@@ -7696,8 +7696,8 @@
       <c r="Y72" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z72" s="9" t="n">
-        <v>0</v>
+      <c r="Z72" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA72" s="10" t="n">
         <v>1</v>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="E73" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" s="6" t="n">
         <v>10</v>
@@ -7793,8 +7793,8 @@
       <c r="Y73" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z73" s="9" t="n">
-        <v>0</v>
+      <c r="Z73" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA73" s="10" t="n">
         <v>1</v>
@@ -7864,7 +7864,7 @@
         <v>1</v>
       </c>
       <c r="Q74" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R74" s="9" t="n">
         <v>0</v>
@@ -8208,7 +8208,7 @@
         </is>
       </c>
       <c r="E78" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F78" s="6" t="n">
         <v>10</v>
@@ -8260,8 +8260,8 @@
       <c r="S78" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T78" s="9" t="n">
-        <v>0</v>
+      <c r="T78" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U78" s="9" t="n">
         <v>0</v>
@@ -8278,8 +8278,8 @@
       <c r="Y78" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z78" s="9" t="n">
-        <v>0</v>
+      <c r="Z78" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA78" s="10" t="n">
         <v>1</v>
@@ -8402,7 +8402,7 @@
         </is>
       </c>
       <c r="E80" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F80" s="6" t="n">
         <v>10</v>
@@ -8472,8 +8472,8 @@
       <c r="Y80" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z80" s="9" t="n">
-        <v>0</v>
+      <c r="Z80" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA80" s="10" t="n">
         <v>1</v>
@@ -8596,7 +8596,7 @@
         </is>
       </c>
       <c r="E82" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F82" s="6" t="n">
         <v>10</v>
@@ -8666,8 +8666,8 @@
       <c r="Y82" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z82" s="9" t="n">
-        <v>0</v>
+      <c r="Z82" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA82" s="10" t="n">
         <v>1</v>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="E83" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F83" s="6" t="n">
         <v>10</v>
@@ -8763,8 +8763,8 @@
       <c r="Y83" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z83" s="9" t="n">
-        <v>0</v>
+      <c r="Z83" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA83" s="10" t="n">
         <v>1</v>
@@ -8790,7 +8790,7 @@
         </is>
       </c>
       <c r="E84" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F84" s="6" t="n">
         <v>10</v>
@@ -8860,8 +8860,8 @@
       <c r="Y84" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z84" s="9" t="n">
-        <v>0</v>
+      <c r="Z84" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA84" s="10" t="n">
         <v>1</v>
@@ -9178,7 +9178,7 @@
         </is>
       </c>
       <c r="E88" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F88" s="6" t="n">
         <v>10</v>
@@ -9219,7 +9219,7 @@
         </is>
       </c>
       <c r="P88" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q88" s="9" t="n">
         <v>0</v>
@@ -9230,8 +9230,8 @@
       <c r="S88" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="T88" s="9" t="n">
-        <v>0</v>
+      <c r="T88" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U88" s="9" t="n">
         <v>0</v>
@@ -9289,13 +9289,13 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L89" s="7" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         <v>0</v>
       </c>
       <c r="V89" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W89" s="9" t="n">
         <v>0</v>
@@ -9677,13 +9677,13 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L93" s="4" t="inlineStr">
         <is>
@@ -9725,7 +9725,7 @@
         <v>4</v>
       </c>
       <c r="W93" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X93" s="10" t="n">
         <v>7</v>
@@ -10065,13 +10065,13 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>3</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L97" s="7" t="inlineStr">
         <is>
@@ -10110,7 +10110,7 @@
         <v>0</v>
       </c>
       <c r="V97" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W97" s="9" t="n">
         <v>0</v>
@@ -10121,8 +10121,8 @@
       <c r="Y97" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z97" s="9" t="n">
-        <v>0</v>
+      <c r="Z97" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA97" s="9" t="n">
         <v>0</v>
@@ -10218,8 +10218,8 @@
       <c r="Y98" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z98" s="9" t="n">
-        <v>0</v>
+      <c r="Z98" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA98" s="9" t="n">
         <v>0</v>
@@ -10412,8 +10412,8 @@
       <c r="Y100" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z100" s="9" t="n">
-        <v>0</v>
+      <c r="Z100" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA100" s="9" t="n">
         <v>0</v>
@@ -10924,7 +10924,7 @@
         </is>
       </c>
       <c r="E106" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F106" s="6" t="n">
         <v>10</v>
@@ -10994,8 +10994,8 @@
       <c r="Y106" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z106" s="9" t="n">
-        <v>0</v>
+      <c r="Z106" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA106" s="10" t="n">
         <v>1</v>
@@ -11021,7 +11021,7 @@
         </is>
       </c>
       <c r="E107" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F107" s="6" t="n">
         <v>10</v>
@@ -11091,8 +11091,8 @@
       <c r="Y107" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z107" s="9" t="n">
-        <v>0</v>
+      <c r="Z107" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA107" s="10" t="n">
         <v>1</v>
@@ -11479,8 +11479,8 @@
       <c r="Y111" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z111" s="9" t="n">
-        <v>0</v>
+      <c r="Z111" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA111" s="9" t="n">
         <v>0</v>
@@ -11547,7 +11547,7 @@
         </is>
       </c>
       <c r="P112" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q112" s="9" t="n">
         <v>0</v>
@@ -11673,8 +11673,8 @@
       <c r="Y113" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z113" s="9" t="n">
-        <v>0</v>
+      <c r="Z113" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA113" s="9" t="n">
         <v>0</v>
@@ -12185,7 +12185,7 @@
         </is>
       </c>
       <c r="E119" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F119" s="6" t="n">
         <v>10</v>
@@ -12237,8 +12237,8 @@
       <c r="S119" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T119" s="9" t="n">
-        <v>0</v>
+      <c r="T119" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U119" s="9" t="n">
         <v>0</v>
@@ -12416,7 +12416,7 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -12449,7 +12449,7 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -12482,7 +12482,7 @@
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -12515,7 +12515,7 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -12548,7 +12548,7 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -12563,7 +12563,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -12581,7 +12581,7 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -12614,7 +12614,7 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -12746,7 +12746,7 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -12779,7 +12779,7 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
         <v>1</v>
@@ -12845,7 +12845,7 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -12878,7 +12878,7 @@
         <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>0.67</v>
+        <v>1.17</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -12911,7 +12911,7 @@
         <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5</v>
+        <v>1.17</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -12944,7 +12944,7 @@
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="E20" t="n">
         <v>1</v>
@@ -13076,7 +13076,7 @@
         <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -13142,7 +13142,7 @@
         <v>6</v>
       </c>
       <c r="D26" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>

--- a/docs/d/222/inyear.xlsx
+++ b/docs/d/222/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:22 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>269 days remain until 30 June 2027, when these scores become final.</t>
+          <t>262 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 13 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 13 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 23 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 23 clubs short</t>
         </is>
       </c>
     </row>
@@ -850,13 +850,13 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>7</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>1</v>
+        <v>-7</v>
       </c>
       <c r="L2" s="7" t="inlineStr">
         <is>
@@ -947,13 +947,13 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="L3" s="7" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>2</v>
       </c>
       <c r="V3" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W3" s="9" t="n">
         <v>0</v>
@@ -1044,13 +1044,13 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>4</v>
       </c>
       <c r="W4" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X4" s="10" t="n">
         <v>7</v>
@@ -1141,17 +1141,17 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M5" s="8" t="n">
@@ -1186,7 +1186,7 @@
         <v>0</v>
       </c>
       <c r="V5" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W5" s="9" t="n">
         <v>0</v>
@@ -1238,13 +1238,13 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L6" s="7" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>0</v>
       </c>
       <c r="V6" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W6" s="9" t="n">
         <v>0</v>
@@ -1335,13 +1335,13 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
@@ -1432,13 +1432,13 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
@@ -1529,13 +1529,13 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
@@ -1626,17 +1626,17 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="L10" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>2</v>
+      </c>
+      <c r="L10" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M10" s="8" t="n">
@@ -1723,17 +1723,17 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>4</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="L11" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>4</v>
+      </c>
+      <c r="L11" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M11" s="8" t="n">
@@ -1820,13 +1820,13 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L12" s="7" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F13" s="6" t="n">
         <v>10</v>
@@ -1917,17 +1917,17 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L13" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L13" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M13" s="8" t="n">
@@ -1961,11 +1961,11 @@
       <c r="U13" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V13" s="9" t="n">
-        <v>3</v>
+      <c r="V13" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W13" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X13" s="10" t="n">
         <v>6</v>
@@ -2014,13 +2014,13 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L14" s="7" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
         <v>0</v>
       </c>
       <c r="V14" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W14" s="9" t="n">
         <v>0</v>
@@ -2111,17 +2111,17 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L15" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M15" s="8" t="n">
@@ -2208,17 +2208,17 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-13</v>
+      </c>
+      <c r="L16" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M16" s="8" t="n">
@@ -2253,7 +2253,7 @@
         <v>0</v>
       </c>
       <c r="V16" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W16" s="9" t="n">
         <v>0</v>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>10</v>
@@ -2305,13 +2305,13 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
@@ -2346,11 +2346,11 @@
       <c r="T17" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U17" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="9" t="n">
-        <v>0</v>
+      <c r="U17" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V17" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W17" s="9" t="n">
         <v>0</v>
@@ -2402,17 +2402,17 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L18" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L18" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M18" s="8" t="n">
@@ -2447,7 +2447,7 @@
         <v>0</v>
       </c>
       <c r="V18" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W18" s="9" t="n">
         <v>0</v>
@@ -2596,13 +2596,13 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" s="7" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>0</v>
       </c>
       <c r="V20" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W20" s="9" t="n">
         <v>0</v>
@@ -2693,17 +2693,17 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L21" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L21" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M21" s="8" t="n">
@@ -2741,7 +2741,7 @@
         <v>4</v>
       </c>
       <c r="W21" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X21" s="9" t="n">
         <v>1</v>
@@ -2790,17 +2790,17 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-13</v>
+      </c>
+      <c r="L22" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M22" s="8" t="n">
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F23" s="6" t="n">
         <v>10</v>
@@ -2931,11 +2931,11 @@
       <c r="U23" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V23" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W23" s="9" t="n">
-        <v>0</v>
+      <c r="V23" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W23" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X23" s="9" t="n">
         <v>1</v>
@@ -2984,13 +2984,13 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>2</v>
+        <v>-10</v>
       </c>
       <c r="L24" s="7" t="inlineStr">
         <is>
@@ -3067,7 +3067,7 @@
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F25" s="6" t="n">
         <v>10</v>
@@ -3081,17 +3081,17 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>5</v>
+      </c>
+      <c r="L25" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M25" s="8" t="n">
@@ -3125,11 +3125,11 @@
       <c r="U25" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V25" s="9" t="n">
-        <v>0</v>
+      <c r="V25" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W25" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X25" s="10" t="n">
         <v>6</v>
@@ -3178,13 +3178,13 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L26" s="7" t="inlineStr">
         <is>
@@ -3275,17 +3275,17 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L27" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M27" s="8" t="n">
@@ -3302,10 +3302,10 @@
         </is>
       </c>
       <c r="P27" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q27" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R27" s="9" t="n">
         <v>0</v>
@@ -3320,7 +3320,7 @@
         <v>0</v>
       </c>
       <c r="V27" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W27" s="9" t="n">
         <v>0</v>
@@ -3469,17 +3469,17 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L29" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>2</v>
+      </c>
+      <c r="L29" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M29" s="8" t="n">
@@ -3663,13 +3663,13 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
         </is>
       </c>
       <c r="P31" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q31" s="9" t="n">
         <v>0</v>
@@ -4051,13 +4051,13 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
@@ -4245,13 +4245,13 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
@@ -4342,13 +4342,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="Q38" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R38" s="9" t="n">
         <v>0</v>
@@ -4522,7 +4522,7 @@
         </is>
       </c>
       <c r="E40" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F40" s="6" t="n">
         <v>10</v>
@@ -4580,8 +4580,8 @@
       <c r="U40" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V40" s="9" t="n">
-        <v>0</v>
+      <c r="V40" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W40" s="9" t="n">
         <v>0</v>
@@ -4716,7 +4716,7 @@
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F42" s="6" t="n">
         <v>10</v>
@@ -4730,17 +4730,17 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L42" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L42" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M42" s="8" t="n">
@@ -4768,8 +4768,8 @@
       <c r="S42" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T42" s="9" t="n">
-        <v>0</v>
+      <c r="T42" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U42" s="9" t="n">
         <v>0</v>
@@ -4827,13 +4827,13 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L43" s="4" t="inlineStr">
         <is>
@@ -5021,13 +5021,13 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
@@ -5118,13 +5118,13 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
@@ -5312,13 +5312,13 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
@@ -5506,13 +5506,13 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
@@ -5603,13 +5603,13 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
@@ -5700,17 +5700,17 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L52" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L52" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M52" s="8" t="n">
@@ -5797,13 +5797,13 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
@@ -5842,7 +5842,7 @@
         <v>0</v>
       </c>
       <c r="V53" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W53" s="9" t="n">
         <v>0</v>
@@ -5894,13 +5894,13 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L54" s="7" t="inlineStr">
         <is>
@@ -5991,17 +5991,17 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-15</v>
+      </c>
+      <c r="L55" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M55" s="8" t="n">
@@ -6036,7 +6036,7 @@
         <v>0</v>
       </c>
       <c r="V55" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W55" s="9" t="n">
         <v>0</v>
@@ -6088,13 +6088,13 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L56" s="7" t="inlineStr">
         <is>
@@ -6133,7 +6133,7 @@
         <v>0</v>
       </c>
       <c r="V56" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W56" s="9" t="n">
         <v>0</v>
@@ -6230,7 +6230,7 @@
         <v>0</v>
       </c>
       <c r="V57" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W57" s="9" t="n">
         <v>0</v>
@@ -6282,17 +6282,17 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="J58" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L58" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-12</v>
+      </c>
+      <c r="L58" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M58" s="8" t="n">
@@ -6379,13 +6379,13 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L59" s="7" t="inlineStr">
         <is>
@@ -6476,17 +6476,17 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L60" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L60" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M60" s="8" t="n">
@@ -6573,13 +6573,13 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
@@ -6656,7 +6656,7 @@
         </is>
       </c>
       <c r="E62" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F62" s="6" t="n">
         <v>10</v>
@@ -6670,13 +6670,13 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L62" s="7" t="inlineStr">
         <is>
@@ -6714,8 +6714,8 @@
       <c r="U62" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V62" s="9" t="n">
-        <v>2</v>
+      <c r="V62" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W62" s="9" t="n">
         <v>0</v>
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
@@ -6812,7 +6812,7 @@
         <v>0</v>
       </c>
       <c r="V63" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W63" s="9" t="n">
         <v>0</v>
@@ -6864,13 +6864,13 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>4</v>
+        <v>-11</v>
       </c>
       <c r="L64" s="4" t="inlineStr">
         <is>
@@ -6900,7 +6900,7 @@
         <v>0</v>
       </c>
       <c r="S64" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T64" s="9" t="n">
         <v>0</v>
@@ -6947,7 +6947,7 @@
         </is>
       </c>
       <c r="E65" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F65" s="6" t="n">
         <v>10</v>
@@ -6961,17 +6961,17 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J65" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L65" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L65" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M65" s="8" t="n">
@@ -6988,7 +6988,7 @@
         </is>
       </c>
       <c r="P65" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q65" s="9" t="n">
         <v>0</v>
@@ -7005,8 +7005,8 @@
       <c r="U65" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V65" s="9" t="n">
-        <v>2</v>
+      <c r="V65" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W65" s="9" t="n">
         <v>0</v>
@@ -7058,13 +7058,13 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="L66" s="4" t="inlineStr">
         <is>
@@ -7106,7 +7106,7 @@
         <v>4</v>
       </c>
       <c r="W66" s="10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X66" s="10" t="n">
         <v>7</v>
@@ -7155,17 +7155,17 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L67" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L67" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M67" s="8" t="n">
@@ -7182,7 +7182,7 @@
         </is>
       </c>
       <c r="P67" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q67" s="9" t="n">
         <v>0</v>
@@ -7297,7 +7297,7 @@
         <v>0</v>
       </c>
       <c r="V68" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W68" s="9" t="n">
         <v>0</v>
@@ -7349,13 +7349,13 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
@@ -7394,7 +7394,7 @@
         <v>0</v>
       </c>
       <c r="V69" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W69" s="9" t="n">
         <v>0</v>
@@ -7446,13 +7446,13 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J70" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L70" s="7" t="inlineStr">
         <is>
@@ -7543,13 +7543,13 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="L71" s="4" t="inlineStr">
         <is>
@@ -7640,13 +7640,13 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="J72" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="L72" s="7" t="inlineStr">
         <is>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="E73" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F73" s="6" t="n">
         <v>10</v>
@@ -7737,13 +7737,13 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L73" s="4" t="inlineStr">
         <is>
@@ -7775,11 +7775,11 @@
       <c r="S73" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T73" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U73" s="9" t="n">
-        <v>0</v>
+      <c r="T73" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U73" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V73" s="9" t="n">
         <v>1</v>
@@ -7834,13 +7834,13 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L74" s="7" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         <v>0</v>
       </c>
       <c r="V74" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W74" s="9" t="n">
         <v>0</v>
@@ -7931,13 +7931,13 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L75" s="7" t="inlineStr">
         <is>
@@ -8028,13 +8028,13 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L76" s="7" t="inlineStr">
         <is>
@@ -8073,7 +8073,7 @@
         <v>0</v>
       </c>
       <c r="V76" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W76" s="9" t="n">
         <v>0</v>
@@ -8125,13 +8125,13 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L77" s="7" t="inlineStr">
         <is>
@@ -8222,17 +8222,17 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L78" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L78" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M78" s="8" t="n">
@@ -8319,17 +8319,17 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L79" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-13</v>
+      </c>
+      <c r="L79" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M79" s="8" t="n">
@@ -8416,13 +8416,13 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>1</v>
+        <v>-7</v>
       </c>
       <c r="L80" s="7" t="inlineStr">
         <is>
@@ -8610,13 +8610,13 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L82" s="4" t="inlineStr">
         <is>
@@ -8655,7 +8655,7 @@
         <v>0</v>
       </c>
       <c r="V82" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W82" s="9" t="n">
         <v>0</v>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="E83" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F83" s="6" t="n">
         <v>10</v>
@@ -8707,13 +8707,13 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L83" s="4" t="inlineStr">
         <is>
@@ -8751,11 +8751,11 @@
       <c r="U83" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V83" s="9" t="n">
-        <v>0</v>
+      <c r="V83" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W83" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X83" s="10" t="n">
         <v>4</v>
@@ -8901,13 +8901,13 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L85" s="4" t="inlineStr">
         <is>
@@ -8998,13 +8998,13 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>7</v>
+        <v>-3</v>
       </c>
       <c r="L86" s="4" t="inlineStr">
         <is>
@@ -9081,7 +9081,7 @@
         </is>
       </c>
       <c r="E87" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F87" s="6" t="n">
         <v>10</v>
@@ -9095,13 +9095,13 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J87" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L87" s="4" t="inlineStr">
         <is>
@@ -9139,11 +9139,11 @@
       <c r="U87" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V87" s="9" t="n">
-        <v>0</v>
+      <c r="V87" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W87" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X87" s="10" t="n">
         <v>4</v>
@@ -9192,13 +9192,13 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L88" s="7" t="inlineStr">
         <is>
@@ -9237,7 +9237,7 @@
         <v>0</v>
       </c>
       <c r="V88" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W88" s="9" t="n">
         <v>0</v>
@@ -9289,13 +9289,13 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L89" s="7" t="inlineStr">
         <is>
@@ -9386,13 +9386,13 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L90" s="4" t="inlineStr">
         <is>
@@ -9483,13 +9483,13 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L91" s="4" t="inlineStr">
         <is>
@@ -9510,7 +9510,7 @@
         </is>
       </c>
       <c r="P91" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q91" s="9" t="n">
         <v>0</v>
@@ -9531,7 +9531,7 @@
         <v>4</v>
       </c>
       <c r="W91" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X91" s="10" t="n">
         <v>6</v>
@@ -9580,13 +9580,13 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J92" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L92" s="7" t="inlineStr">
         <is>
@@ -9677,13 +9677,13 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>7</v>
+        <v>-1</v>
       </c>
       <c r="L93" s="4" t="inlineStr">
         <is>
@@ -9774,13 +9774,13 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L94" s="4" t="inlineStr">
         <is>
@@ -9871,17 +9871,17 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="J95" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L95" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L95" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M95" s="8" t="n">
@@ -9919,7 +9919,7 @@
         <v>4</v>
       </c>
       <c r="W95" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X95" s="10" t="n">
         <v>4</v>
@@ -9968,13 +9968,13 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L96" s="7" t="inlineStr">
         <is>
@@ -10051,7 +10051,7 @@
         </is>
       </c>
       <c r="E97" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F97" s="6" t="n">
         <v>10</v>
@@ -10065,17 +10065,17 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>3</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L97" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>5</v>
+      </c>
+      <c r="L97" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M97" s="8" t="n">
@@ -10109,11 +10109,11 @@
       <c r="U97" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V97" s="9" t="n">
-        <v>1</v>
+      <c r="V97" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W97" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X97" s="9" t="n">
         <v>0</v>
@@ -10162,13 +10162,13 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J98" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L98" s="7" t="inlineStr">
         <is>
@@ -10207,7 +10207,7 @@
         <v>0</v>
       </c>
       <c r="V98" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W98" s="9" t="n">
         <v>0</v>
@@ -10259,13 +10259,13 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>6</v>
+        <v>-4</v>
       </c>
       <c r="L99" s="4" t="inlineStr">
         <is>
@@ -10307,7 +10307,7 @@
         <v>4</v>
       </c>
       <c r="W99" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X99" s="10" t="n">
         <v>6</v>
@@ -10342,7 +10342,7 @@
         </is>
       </c>
       <c r="E100" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F100" s="6" t="n">
         <v>10</v>
@@ -10356,13 +10356,13 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L100" s="7" t="inlineStr">
         <is>
@@ -10400,8 +10400,8 @@
       <c r="U100" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V100" s="9" t="n">
-        <v>0</v>
+      <c r="V100" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W100" s="9" t="n">
         <v>0</v>
@@ -10453,13 +10453,13 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L101" s="7" t="inlineStr">
         <is>
@@ -10550,17 +10550,17 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L102" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L102" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M102" s="8" t="n">
@@ -10633,7 +10633,7 @@
         </is>
       </c>
       <c r="E103" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F103" s="6" t="n">
         <v>10</v>
@@ -10647,13 +10647,13 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J103" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L103" s="4" t="inlineStr">
         <is>
@@ -10694,8 +10694,8 @@
       <c r="V103" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W103" s="9" t="n">
-        <v>0</v>
+      <c r="W103" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X103" s="10" t="n">
         <v>5</v>
@@ -10744,13 +10744,13 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J104" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L104" s="7" t="inlineStr">
         <is>
@@ -10789,7 +10789,7 @@
         <v>0</v>
       </c>
       <c r="V104" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W104" s="9" t="n">
         <v>0</v>
@@ -10841,13 +10841,13 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L105" s="7" t="inlineStr">
         <is>
@@ -10938,13 +10938,13 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
       <c r="L106" s="7" t="inlineStr">
         <is>
@@ -10968,7 +10968,7 @@
         <v>0</v>
       </c>
       <c r="Q106" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R106" s="9" t="n">
         <v>0</v>
@@ -11035,13 +11035,13 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J107" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L107" s="7" t="inlineStr">
         <is>
@@ -11080,7 +11080,7 @@
         <v>0</v>
       </c>
       <c r="V107" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W107" s="9" t="n">
         <v>0</v>
@@ -11132,13 +11132,13 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L108" s="7" t="inlineStr">
         <is>
@@ -11229,13 +11229,13 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L109" s="7" t="inlineStr">
         <is>
@@ -11326,17 +11326,17 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L110" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-22</v>
+      </c>
+      <c r="L110" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M110" s="8" t="n">
@@ -11423,13 +11423,13 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L111" s="7" t="inlineStr">
         <is>
@@ -11450,7 +11450,7 @@
         </is>
       </c>
       <c r="P111" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q111" s="10" t="n">
         <v>2</v>
@@ -11506,7 +11506,7 @@
         </is>
       </c>
       <c r="E112" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F112" s="6" t="n">
         <v>10</v>
@@ -11520,17 +11520,17 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="J112" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L112" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L112" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M112" s="8" t="n">
@@ -11547,28 +11547,28 @@
         </is>
       </c>
       <c r="P112" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q112" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R112" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S112" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T112" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U112" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V112" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W112" s="9" t="n">
         <v>2</v>
-      </c>
-      <c r="Q112" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R112" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S112" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T112" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U112" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V112" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="W112" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="X112" s="10" t="n">
         <v>6</v>
@@ -11603,7 +11603,7 @@
         </is>
       </c>
       <c r="E113" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F113" s="6" t="n">
         <v>10</v>
@@ -11617,13 +11617,13 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J113" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L113" s="4" t="inlineStr">
         <is>
@@ -11661,11 +11661,11 @@
       <c r="U113" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V113" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W113" s="9" t="n">
-        <v>0</v>
+      <c r="V113" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W113" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X113" s="9" t="n">
         <v>1</v>
@@ -11714,13 +11714,13 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J114" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L114" s="7" t="inlineStr">
         <is>
@@ -11759,7 +11759,7 @@
         <v>2</v>
       </c>
       <c r="V114" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W114" s="9" t="n">
         <v>0</v>
@@ -11908,13 +11908,13 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J116" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="L116" s="7" t="inlineStr">
         <is>
@@ -12005,13 +12005,13 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J117" s="4" t="n">
         <v>5</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L117" s="7" t="inlineStr">
         <is>
@@ -12088,7 +12088,7 @@
         </is>
       </c>
       <c r="E118" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F118" s="6" t="n">
         <v>10</v>
@@ -12102,13 +12102,13 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="J118" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>3</v>
+        <v>-9</v>
       </c>
       <c r="L118" s="4" t="inlineStr">
         <is>
@@ -12146,8 +12146,8 @@
       <c r="U118" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V118" s="9" t="n">
-        <v>3</v>
+      <c r="V118" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W118" s="9" t="n">
         <v>0</v>
@@ -12199,13 +12199,13 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J119" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K119" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L119" s="4" t="inlineStr">
         <is>
@@ -12365,7 +12365,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -12416,13 +12416,13 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -12431,7 +12431,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -12449,13 +12449,13 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -12464,7 +12464,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -12482,7 +12482,7 @@
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5</v>
+        <v>0.83</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -12497,7 +12497,7 @@
         <v>3</v>
       </c>
       <c r="I6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -12515,7 +12515,7 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -12563,7 +12563,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -12647,7 +12647,7 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -12662,7 +12662,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -12728,7 +12728,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -12761,7 +12761,7 @@
         <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -12779,7 +12779,7 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E15" t="n">
         <v>1</v>
@@ -12794,7 +12794,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -12812,7 +12812,7 @@
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -12827,7 +12827,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -12878,7 +12878,7 @@
         <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>1.17</v>
+        <v>1.5</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -12893,7 +12893,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -12911,7 +12911,7 @@
         <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -12926,7 +12926,7 @@
         <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -12944,7 +12944,7 @@
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="E20" t="n">
         <v>1</v>
@@ -13010,7 +13010,7 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -13043,7 +13043,7 @@
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -13058,7 +13058,7 @@
         <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -13109,7 +13109,7 @@
         <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -13124,7 +13124,7 @@
         <v>2</v>
       </c>
       <c r="I25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -13142,7 +13142,7 @@
         <v>6</v>
       </c>
       <c r="D26" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>

--- a/docs/d/222/inyear.xlsx
+++ b/docs/d/222/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/222/inyear.xlsx
+++ b/docs/d/222/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/222/inyear.xlsx
+++ b/docs/d/222/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/222/inyear.xlsx
+++ b/docs/d/222/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/222/inyear.xlsx
+++ b/docs/d/222/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 13 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 13 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 23 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 23 clubs short</t>
         </is>
       </c>
     </row>
@@ -1044,13 +1044,13 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>4</v>
       </c>
       <c r="W4" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X4" s="10" t="n">
         <v>7</v>
@@ -1268,7 +1268,7 @@
         <v>0</v>
       </c>
       <c r="Q6" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" s="9" t="n">
         <v>0</v>
@@ -1917,13 +1917,13 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
@@ -2014,13 +2014,13 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L14" s="7" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         <v>1</v>
       </c>
       <c r="Q17" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" s="9" t="n">
         <v>0</v>
@@ -2388,7 +2388,7 @@
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F18" s="6" t="n">
         <v>10</v>
@@ -2440,8 +2440,8 @@
       <c r="S18" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T18" s="9" t="n">
-        <v>0</v>
+      <c r="T18" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U18" s="9" t="n">
         <v>0</v>
@@ -2623,7 +2623,7 @@
         </is>
       </c>
       <c r="P20" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q20" s="9" t="n">
         <v>1</v>
@@ -4148,13 +4148,13 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36" s="7" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         <v>0</v>
       </c>
       <c r="V36" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W36" s="9" t="n">
         <v>0</v>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="P42" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q42" s="9" t="n">
         <v>0</v>
@@ -5492,7 +5492,7 @@
         </is>
       </c>
       <c r="E50" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F50" s="6" t="n">
         <v>10</v>
@@ -5544,8 +5544,8 @@
       <c r="S50" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T50" s="9" t="n">
-        <v>0</v>
+      <c r="T50" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U50" s="9" t="n">
         <v>0</v>
@@ -6379,13 +6379,13 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L59" s="7" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
         <v>0</v>
       </c>
       <c r="V59" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W59" s="9" t="n">
         <v>0</v>
@@ -6850,7 +6850,7 @@
         </is>
       </c>
       <c r="E64" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F64" s="6" t="n">
         <v>10</v>
@@ -6899,8 +6899,8 @@
       <c r="R64" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S64" s="9" t="n">
-        <v>1</v>
+      <c r="S64" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T64" s="9" t="n">
         <v>0</v>
@@ -6961,13 +6961,13 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J65" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
@@ -7200,7 +7200,7 @@
         <v>0</v>
       </c>
       <c r="V67" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W67" s="9" t="n">
         <v>0</v>
@@ -7252,13 +7252,13 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L68" s="7" t="inlineStr">
         <is>
@@ -7737,13 +7737,13 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L73" s="4" t="inlineStr">
         <is>
@@ -7782,7 +7782,7 @@
         <v>1</v>
       </c>
       <c r="V73" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W73" s="9" t="n">
         <v>0</v>
@@ -7931,13 +7931,13 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L75" s="7" t="inlineStr">
         <is>
@@ -8125,13 +8125,13 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L77" s="7" t="inlineStr">
         <is>
@@ -8222,13 +8222,13 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>-9</v>
+        <v>-7</v>
       </c>
       <c r="L78" s="7" t="inlineStr">
         <is>
@@ -8790,7 +8790,7 @@
         </is>
       </c>
       <c r="E84" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F84" s="6" t="n">
         <v>10</v>
@@ -8842,8 +8842,8 @@
       <c r="S84" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T84" s="9" t="n">
-        <v>0</v>
+      <c r="T84" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U84" s="9" t="n">
         <v>0</v>
@@ -8887,7 +8887,7 @@
         </is>
       </c>
       <c r="E85" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F85" s="6" t="n">
         <v>10</v>
@@ -8942,8 +8942,8 @@
       <c r="T85" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U85" s="9" t="n">
-        <v>0</v>
+      <c r="U85" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V85" s="9" t="n">
         <v>0</v>
@@ -8984,7 +8984,7 @@
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F86" s="6" t="n">
         <v>10</v>
@@ -8998,13 +8998,13 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L86" s="4" t="inlineStr">
         <is>
@@ -9027,8 +9027,8 @@
       <c r="P86" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="Q86" s="9" t="n">
-        <v>1</v>
+      <c r="Q86" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R86" s="9" t="n">
         <v>0</v>
@@ -9871,13 +9871,13 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J95" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L95" s="7" t="inlineStr">
         <is>
@@ -10245,7 +10245,7 @@
         </is>
       </c>
       <c r="E99" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F99" s="6" t="n">
         <v>10</v>
@@ -10259,13 +10259,13 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L99" s="4" t="inlineStr">
         <is>
@@ -10306,8 +10306,8 @@
       <c r="V99" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W99" s="9" t="n">
-        <v>3</v>
+      <c r="W99" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X99" s="10" t="n">
         <v>6</v>
@@ -10356,13 +10356,13 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L100" s="7" t="inlineStr">
         <is>
@@ -10404,7 +10404,7 @@
         <v>4</v>
       </c>
       <c r="W100" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X100" s="10" t="n">
         <v>5</v>
@@ -11423,13 +11423,13 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L111" s="7" t="inlineStr">
         <is>
@@ -12102,13 +12102,13 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J118" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L118" s="4" t="inlineStr">
         <is>
@@ -12150,7 +12150,7 @@
         <v>4</v>
       </c>
       <c r="W118" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X118" s="10" t="n">
         <v>7</v>
@@ -12482,7 +12482,7 @@
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -12713,7 +12713,7 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -12812,7 +12812,7 @@
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -12911,7 +12911,7 @@
         <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -12944,7 +12944,7 @@
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="E20" t="n">
         <v>1</v>
@@ -13010,13 +13010,13 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>

--- a/docs/d/222/inyear.xlsx
+++ b/docs/d/222/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:50 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 13 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (67 days) - 13 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 23 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 23 clubs short</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
         </is>
       </c>
       <c r="E3" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3" s="6" t="n">
         <v>10</v>
@@ -976,8 +976,8 @@
       <c r="P3" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q3" s="9" t="n">
-        <v>1</v>
+      <c r="Q3" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R3" s="9" t="n">
         <v>0</v>
@@ -1044,13 +1044,13 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
@@ -1071,16 +1071,16 @@
         </is>
       </c>
       <c r="P4" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q4" s="10" t="n">
         <v>2</v>
       </c>
       <c r="R4" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S4" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T4" s="10" t="n">
         <v>1</v>
@@ -1092,7 +1092,7 @@
         <v>4</v>
       </c>
       <c r="W4" s="10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X4" s="10" t="n">
         <v>7</v>
@@ -1626,13 +1626,13 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L10" s="7" t="inlineStr">
         <is>
@@ -1726,10 +1726,10 @@
         <v>8</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
@@ -2305,13 +2305,13 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
         <v>4</v>
       </c>
       <c r="W17" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X17" s="10" t="n">
         <v>6</v>
@@ -2623,7 +2623,7 @@
         </is>
       </c>
       <c r="P20" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q20" s="9" t="n">
         <v>1</v>
@@ -2693,17 +2693,17 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-2</v>
-      </c>
-      <c r="L21" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M21" s="8" t="n">
@@ -2741,7 +2741,7 @@
         <v>4</v>
       </c>
       <c r="W21" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X21" s="9" t="n">
         <v>1</v>
@@ -2914,7 +2914,7 @@
         </is>
       </c>
       <c r="P23" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q23" s="9" t="n">
         <v>0</v>
@@ -2984,13 +2984,13 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L24" s="7" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         </is>
       </c>
       <c r="P25" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q25" s="9" t="n">
         <v>1</v>
@@ -3261,7 +3261,7 @@
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F27" s="6" t="n">
         <v>10</v>
@@ -3301,8 +3301,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P27" s="9" t="n">
-        <v>3</v>
+      <c r="P27" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q27" s="9" t="n">
         <v>1</v>
@@ -3566,13 +3566,13 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L30" s="7" t="inlineStr">
         <is>
@@ -3611,7 +3611,7 @@
         <v>0</v>
       </c>
       <c r="V30" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W30" s="9" t="n">
         <v>0</v>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="P39" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q39" s="9" t="n">
         <v>0</v>
@@ -5339,7 +5339,7 @@
         </is>
       </c>
       <c r="P48" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q48" s="9" t="n">
         <v>0</v>
@@ -5542,7 +5542,7 @@
         <v>0</v>
       </c>
       <c r="S50" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T50" s="10" t="n">
         <v>1</v>
@@ -6753,7 +6753,7 @@
         </is>
       </c>
       <c r="E63" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F63" s="6" t="n">
         <v>10</v>
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
@@ -6805,8 +6805,8 @@
       <c r="S63" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T63" s="9" t="n">
-        <v>0</v>
+      <c r="T63" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U63" s="9" t="n">
         <v>0</v>
@@ -6991,7 +6991,7 @@
         <v>1</v>
       </c>
       <c r="Q65" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R65" s="9" t="n">
         <v>0</v>
@@ -7185,7 +7185,7 @@
         <v>1</v>
       </c>
       <c r="Q67" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R67" s="9" t="n">
         <v>0</v>
@@ -7252,13 +7252,13 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L68" s="7" t="inlineStr">
         <is>
@@ -7297,7 +7297,7 @@
         <v>0</v>
       </c>
       <c r="V68" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W68" s="9" t="n">
         <v>0</v>
@@ -8225,10 +8225,10 @@
         <v>13</v>
       </c>
       <c r="J78" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="L78" s="7" t="inlineStr">
         <is>
@@ -9025,7 +9025,7 @@
         </is>
       </c>
       <c r="P86" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q86" s="10" t="n">
         <v>2</v>
@@ -9275,7 +9275,7 @@
         </is>
       </c>
       <c r="E89" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F89" s="6" t="n">
         <v>10</v>
@@ -9289,13 +9289,13 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L89" s="7" t="inlineStr">
         <is>
@@ -9333,11 +9333,11 @@
       <c r="U89" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V89" s="9" t="n">
-        <v>3</v>
+      <c r="V89" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W89" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X89" s="10" t="n">
         <v>7</v>
@@ -9486,10 +9486,10 @@
         <v>37</v>
       </c>
       <c r="J91" s="4" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L91" s="4" t="inlineStr">
         <is>
@@ -9874,10 +9874,10 @@
         <v>15</v>
       </c>
       <c r="J95" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="L95" s="7" t="inlineStr">
         <is>
@@ -10259,13 +10259,13 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="L99" s="4" t="inlineStr">
         <is>
@@ -10286,13 +10286,13 @@
         </is>
       </c>
       <c r="P99" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q99" s="10" t="n">
         <v>2</v>
       </c>
       <c r="R99" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S99" s="9" t="n">
         <v>0</v>
@@ -10307,7 +10307,7 @@
         <v>4</v>
       </c>
       <c r="W99" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="X99" s="10" t="n">
         <v>6</v>
@@ -11132,13 +11132,13 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L108" s="7" t="inlineStr">
         <is>
@@ -11177,7 +11177,7 @@
         <v>0</v>
       </c>
       <c r="V108" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W108" s="9" t="n">
         <v>0</v>
@@ -11409,7 +11409,7 @@
         </is>
       </c>
       <c r="E111" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F111" s="6" t="n">
         <v>10</v>
@@ -11461,8 +11461,8 @@
       <c r="S111" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T111" s="9" t="n">
-        <v>0</v>
+      <c r="T111" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U111" s="9" t="n">
         <v>0</v>
@@ -12350,7 +12350,7 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -12497,7 +12497,7 @@
         <v>3</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -12515,7 +12515,7 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -12812,7 +12812,7 @@
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -12944,7 +12944,7 @@
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="E20" t="n">
         <v>1</v>
@@ -13109,7 +13109,7 @@
         <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
